--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 침산점</t>
+          <t>바디엔지니어스짐 동구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>body7677@naver.com</t>
+          <t>catess110@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1388-7681</t>
+          <t>0507-1493-7680</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 3층 바디엔지니어스짐 침산점</t>
+          <t>대구 동구 안심로 266 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineers_kr</t>
+          <t>https://blog.naver.com/catess110</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1436</v>
+        <v>766</v>
       </c>
       <c r="Q2" t="n">
-        <v>1921</v>
+        <v>1313</v>
       </c>
       <c r="R2" t="n">
-        <v>3357</v>
+        <v>2079</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,47 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1961345457</t>
+          <t>77223878</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1961345457</t>
+          <t>https://m.place.naver.com/place/77223878</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
+          <t>노바짐 헬스&amp;PT 달서구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atmhjqnib@naver.com</t>
+          <t>nova__gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1341-2034</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
+          <t>대구 달서구 장기로 217 8, 9층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atmhjqnib</t>
+          <t>https://blog.naver.com/nova__gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +696,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ttpt</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1185</v>
+        <v>346</v>
       </c>
       <c r="Q3" t="n">
-        <v>552</v>
+        <v>442</v>
       </c>
       <c r="R3" t="n">
-        <v>1737</v>
+        <v>788</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>671730517</t>
+          <t>1731760179</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/671730517</t>
+          <t>https://m.place.naver.com/place/1731760179</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>옐로우짐 만촌역점 헬스&amp;PT&amp;필라테스&amp;요가&amp;줌바</t>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yellowgym13@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1436-0078</t>
+          <t>0507-1341-2034</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 달구벌대로 2575 영원무역 대구빌딩 3층, 4층</t>
+          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yellowgym13</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdal64e</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1346</v>
+        <v>1194</v>
       </c>
       <c r="Q4" t="n">
-        <v>613</v>
+        <v>558</v>
       </c>
       <c r="R4" t="n">
-        <v>1959</v>
+        <v>1752</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,56 +828,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1035761617</t>
+          <t>671730517</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1035761617</t>
+          <t>https://m.place.naver.com/place/671730517</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 헬스&amp;PT 수성점</t>
+          <t>피트온24 범어점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chl3503@naver.com</t>
+          <t>fiton24_beomeo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1491-7677</t>
+          <t>053-759-3166</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 청수로26길 36 한성스퀘어 5층</t>
+          <t>대구 수성구 범어천로 214 더리브 503-507호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://boddy.imweb.me/</t>
+          <t>https://www.instagram.com/fiton24_beomeo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,15 +887,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tu6f</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>943</v>
+        <v>2339</v>
       </c>
       <c r="Q5" t="n">
-        <v>1282</v>
+        <v>986</v>
       </c>
       <c r="R5" t="n">
-        <v>2225</v>
+        <v>3325</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +926,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1885094891</t>
+          <t>1328042225</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885094891</t>
+          <t>https://m.place.naver.com/place/1328042225</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>지젤 죽전점 헬스 PT</t>
+          <t>스톤짐 남산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>giselle3317@naver.com</t>
+          <t>nb99022@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1407-7936</t>
+          <t>053-424-4001</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 달서구 와룡로 169 대우 월드마크웨스트엔드상가 106동 201호</t>
+          <t>대구 중구 달구벌대로 2012 13층 (11, 13, 14층)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/giselle3317/223974664270</t>
+          <t>https://www.instagram.com/stonegym_namsan</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +985,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wogaee9</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1885</v>
+        <v>290</v>
       </c>
       <c r="Q6" t="n">
-        <v>766</v>
+        <v>86</v>
       </c>
       <c r="R6" t="n">
-        <v>2651</v>
+        <v>376</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1024,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>56046213</t>
+          <t>2027766732</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/56046213</t>
+          <t>https://m.place.naver.com/place/2027766732</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+          <t>몰리짐 중동교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hannover_reha@naver.com</t>
+          <t>mollygym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1378-5757</t>
+          <t>0507-1498-9683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 중구 공평로8길 11-1 3층</t>
+          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://hanover.co.kr</t>
+          <t>http://pf.kakao.com/_lxhpxns</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,13 +1088,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4muzo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>409</v>
+        <v>798</v>
       </c>
       <c r="Q7" t="n">
-        <v>2021</v>
+        <v>1269</v>
       </c>
       <c r="R7" t="n">
-        <v>2430</v>
+        <v>2067</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1122,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1113071233</t>
+          <t>1614047956</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1113071233</t>
+          <t>https://m.place.naver.com/place/1614047956</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>국민피티 침산점</t>
+          <t>WR웰니스짐 수성 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kukminpt@naver.com</t>
+          <t>wr_premium_fit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1398-9797</t>
+          <t>0507-1386-9688</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 이마트 6층 하늘정원</t>
+          <t>대구 수성구 동대구로 44 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kukminpt</t>
+          <t>https://blog.naver.com/wr_premium_fit</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1181,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d3lf</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>697</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
-        <v>779</v>
+        <v>731</v>
       </c>
       <c r="R8" t="n">
-        <v>1476</v>
+        <v>1035</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1636758988</t>
+          <t>1407080934</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636758988</t>
+          <t>https://m.place.naver.com/place/1407080934</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피트온24 범어점</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fiton24_beomeo@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>053-759-3166</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 범어천로 214 더리브 503-507호</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fiton24_beomeo</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1264,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2339</v>
+        <v>103</v>
       </c>
       <c r="Q9" t="n">
-        <v>896</v>
+        <v>329</v>
       </c>
       <c r="R9" t="n">
-        <v>3235</v>
+        <v>432</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1328042225</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328042225</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>시너지피트니스 수성점</t>
+          <t>유케이 짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kja931209@naver.com</t>
+          <t>ukgym_official@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1365-7677</t>
+          <t>0507-1399-1895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 수성로75길 16 제401동 103호</t>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/synergy.suseong</t>
+          <t>https://blog.naver.com/ukgym_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,15 +1377,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>964</v>
+        <v>236</v>
       </c>
       <c r="Q10" t="n">
-        <v>1244</v>
+        <v>135</v>
       </c>
       <c r="R10" t="n">
-        <v>2208</v>
+        <v>371</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1416,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1125888116</t>
+          <t>1054343439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125888116</t>
+          <t>https://m.place.naver.com/place/1054343439</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피트온24 중동점</t>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fiton24_jd@naver.com</t>
+          <t>hannover_reha@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1395-8629</t>
+          <t>0507-1378-5757</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 수성로 212 광원빌딩 3층 피트온24 중동점</t>
+          <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fiton24_jd</t>
+          <t>https://hanover.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,15 +1475,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r74y</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1611</v>
+        <v>419</v>
       </c>
       <c r="Q11" t="n">
-        <v>800</v>
+        <v>2096</v>
       </c>
       <c r="R11" t="n">
-        <v>2411</v>
+        <v>2515</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1472735445</t>
+          <t>1113071233</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472735445</t>
+          <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1536,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피트온24 남산점</t>
+          <t>국민피티 침산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>yougung93@naver.com</t>
+          <t>kukminpt@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>053-655-9677</t>
+          <t>0507-1398-9797</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 남구 명덕로 120</t>
+          <t>대구 북구 침산로 93 이마트 6층 하늘정원</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kukminpt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1536,7 +1568,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1546,10 +1578,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f9se</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1557,17 +1593,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>989</v>
+        <v>701</v>
       </c>
       <c r="Q12" t="n">
-        <v>802</v>
+        <v>1015</v>
       </c>
       <c r="R12" t="n">
-        <v>1791</v>
+        <v>1716</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,863 +1612,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1054239476</t>
+          <t>1636758988</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054239476</t>
+          <t>https://m.place.naver.com/place/1636758988</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>피트온24 복현점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>mave000@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1322-3225</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대구광역시 북구 동북로 279 세림빌딩(신협건물)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/mave000</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>895</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2911</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1855565865</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1855565865</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>피트온24 칠곡점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>fitness240@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>053-313-8817</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>대구광역시 북구 학정로 416 4층 피트온24</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fitness240</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>2303</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>882</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3185</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1175448883</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1175448883</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>피트온24 범물점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>be_hyepppy@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1322-1947</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>대구광역시 수성구 지범로 174 B1층 피트온24 범물점</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/fiton24_</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>2600</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>941</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3541</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1109268327</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1109268327</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>짐 엘리트&amp;스파 진천점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ejrtks16@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1444-0569</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>대구광역시 달서구 월배로 80 대성스카이렉스 2층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ejrtks16/224172936183</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>990</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>719</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1709</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1498248838</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1498248838</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>더 월드짐</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>theworldgym_@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1488-9697</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>대구광역시 수성구 명덕로 404 한성빌딩 10F</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/twg__suseong/</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>283</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1039</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1322</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1302496262</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1302496262</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>원나인피트니스</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>fhdnzlr892@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1800-6672</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>대구광역시 북구 호암로 6 5층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fhdnzlr892</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>193</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>576</v>
-      </c>
-      <c r="R18" t="n">
-        <v>769</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1696346241</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1696346241</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>피트온24 대봉점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>fiton24_daebong@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1319-8731</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>대구광역시 중구 동덕로 55 대봉태왕아너스 상가 지하1층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/fiton24_daebong/</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1711</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>769</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2480</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1862533516</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1862533516</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>우드짐 WOOD GYM</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>eastok7@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1308-5832</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>대구광역시 수성구 수성로 412 한국씨티은행 건물 119동 3층 301호</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>239</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>66</v>
-      </c>
-      <c r="R20" t="n">
-        <v>305</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1890166927</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1890166927</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>F45 달서</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2polvoron@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1361-4548</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>대구광역시 달서구 조암로 17 7층 F45달서</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/f45_dalseo</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>766</v>
-      </c>
-      <c r="R21" t="n">
-        <v>894</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1596688973</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1596688973</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/catess110</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heesangi2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         <v>104</v>
       </c>
       <c r="Q3" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="R3" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atmhjqnib@naver.com</t>
+          <t>ptdaniel@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atmhjqnib</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mollygym_vol.3/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fiton24_beomeo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1110,10 +1110,10 @@
         <v>2340</v>
       </c>
       <c r="Q7" t="n">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="R7" t="n">
-        <v>3328</v>
+        <v>3330</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>위즈고 헬스&amp;PT 시지점</t>
+          <t>몰리짐 중동교점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>woojung4545@naver.com</t>
+          <t>mollygym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1305-6676</t>
+          <t>0507-1498-9683</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 수성구 신매로19길 56 4층 5층</t>
+          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/woojung4545</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmrepxn</t>
+          <t>https://talk.naver.com/ct/w4muzo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>389</v>
+        <v>803</v>
       </c>
       <c r="Q8" t="n">
-        <v>330</v>
+        <v>1269</v>
       </c>
       <c r="R8" t="n">
-        <v>719</v>
+        <v>2072</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1586786552</t>
+          <t>1614047956</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1586786552</t>
+          <t>https://m.place.naver.com/place/1614047956</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1242,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피크짐 신천점</t>
+          <t>국민피티 월배점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>peakgym2022@naver.com</t>
+          <t>kukminptwolbae@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1355-6339</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 동구 장등로 66 1층</t>
+          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/peakgym2022</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,24 +1270,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9noycr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,17 +1291,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>488</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="R9" t="n">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1310,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1934353498</t>
+          <t>1009333460</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934353498</t>
+          <t>https://m.place.naver.com/place/1009333460</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>위즈고 헬스&amp;PT 시지점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>hanyang0226@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1305-6676</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 수성구 신매로19길 56 4층 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,7 +1364,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1387,27 +1379,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/wmrepxn</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>103</v>
+        <v>389</v>
       </c>
       <c r="Q10" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R10" t="n">
-        <v>432</v>
+        <v>719</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,51 +1408,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>1586786552</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/1586786552</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유케이 짐</t>
+          <t>피크짐 신천점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ukgym_official@naver.com</t>
+          <t>peakgym2022@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-1895</t>
+          <t>0507-1355-6339</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+          <t>대구 동구 장등로 66 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ukgym_official</t>
+          <t>https://blog.naver.com/peakgym2022</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1477,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxm7p20</t>
+          <t>https://talk.naver.com/ct/w9noycr</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,17 +1487,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>236</v>
+        <v>487</v>
       </c>
       <c r="Q11" t="n">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="R11" t="n">
-        <v>373</v>
+        <v>549</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,115 +1506,311 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1054343439</t>
+          <t>1934353498</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
+          <t>https://m.place.naver.com/place/1934353498</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hannover_reha@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1378-5757</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>329</v>
+      </c>
+      <c r="R12" t="n">
+        <v>432</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1701902663</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1701902663</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>유케이 짐</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ukgym_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1399-1895</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>137</v>
+      </c>
+      <c r="R13" t="n">
+        <v>373</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1054343439</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054343439</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hannover_reha@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1378-5757</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://hanover.co.kr</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4r74y</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>420</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2112</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2532</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="Q14" t="n">
+        <v>2120</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2540</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>1113071233</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 동구점</t>
+          <t>노바짐 헬스&amp;PT 달서구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>catess110@naver.com</t>
+          <t>nova__gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1493-7680</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 동구 안심로 266 4층</t>
+          <t>대구 달서구 장기로 217 8, 9층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nova__gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +592,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ttpt</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>767</v>
+        <v>346</v>
       </c>
       <c r="Q2" t="n">
-        <v>1313</v>
+        <v>442</v>
       </c>
       <c r="R2" t="n">
-        <v>2080</v>
+        <v>788</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>77223878</t>
+          <t>1731760179</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/77223878</t>
+          <t>https://m.place.naver.com/place/1731760179</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/heesangi2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -722,10 +722,10 @@
         <v>104</v>
       </c>
       <c r="Q3" t="n">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="R3" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ptdaniel@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -820,10 +820,10 @@
         <v>1194</v>
       </c>
       <c r="Q4" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="R4" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -849,34 +849,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+          <t>헬스&amp;PT 몰리짐 장기점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>giselle331704@naver.com</t>
+          <t>mollygym_vol3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1321-6496</t>
+          <t>0507-1469-9682</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 북구 동암로 90 3층</t>
+          <t>대구 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mollygym_vol.3/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -896,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t9mv</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1241</v>
+        <v>1080</v>
       </c>
       <c r="Q5" t="n">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="R5" t="n">
-        <v>1785</v>
+        <v>1626</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1616049160</t>
+          <t>1048460846</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616049160</t>
+          <t>https://m.place.naver.com/place/1048460846</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -943,34 +947,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 몰리짐 장기점</t>
+          <t>지젤 칠곡점 헬스 PT GX 요가</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mollygym_vol3@naver.com</t>
+          <t>giselle331704@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1469-9682</t>
+          <t>0507-1321-6496</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 달서구 용산로 80 에이동</t>
+          <t>대구 북구 동암로 90 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +984,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,14 +994,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5t9mv</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1080</v>
+        <v>1241</v>
       </c>
       <c r="Q6" t="n">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="R6" t="n">
-        <v>1626</v>
+        <v>1785</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1048460846</t>
+          <t>1616049160</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048460846</t>
+          <t>https://m.place.naver.com/place/1616049160</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,29 +1046,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트온24 범어점</t>
+          <t>레드짐 동성로점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fiton24_beomeo@naver.com</t>
+          <t>redgym_dongseongro@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>053-759-3166</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 수성구 범어천로 214 더리브 503-507호</t>
+          <t>대구 중구 동성로2길 95 지하1, 2층 B101, B201호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/redgym_dongseongro</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,7 +1074,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1093,7 +1089,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tu6f</t>
+          <t>https://talk.naver.com/ct/w5xyzh</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2340</v>
+        <v>395</v>
       </c>
       <c r="Q7" t="n">
-        <v>990</v>
+        <v>393</v>
       </c>
       <c r="R7" t="n">
-        <v>3330</v>
+        <v>788</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1118,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1328042225</t>
+          <t>1444163779</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328042225</t>
+          <t>https://m.place.naver.com/place/1444163779</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1166,17 +1162,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_lxhpxns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1237,30 +1233,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>국민피티 월배점</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kukminptwolbae@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1356-4013</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1280,10 +1280,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="Q9" t="n">
-        <v>184</v>
+        <v>329</v>
       </c>
       <c r="R9" t="n">
-        <v>211</v>
+        <v>432</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1009333460</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1327,34 +1331,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>위즈고 헬스&amp;PT 시지점</t>
+          <t>유케이 짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hanyang0226@naver.com</t>
+          <t>ukgym_official@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1305-6676</t>
+          <t>0507-1399-1895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 신매로19길 56 4층 5층</t>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ukgym_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1364,12 +1368,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1379,27 +1383,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmrepxn</t>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>389</v>
+        <v>236</v>
       </c>
       <c r="Q10" t="n">
-        <v>330</v>
+        <v>137</v>
       </c>
       <c r="R10" t="n">
-        <v>719</v>
+        <v>373</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1586786552</t>
+          <t>1054343439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1586786552</t>
+          <t>https://m.place.naver.com/place/1054343439</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1425,34 +1429,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피크짐 신천점</t>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>peakgym2022@naver.com</t>
+          <t>hannover_reha@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1355-6339</t>
+          <t>0507-1378-5757</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 동구 장등로 66 1층</t>
+          <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/peakgym2022</t>
+          <t>https://hanover.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1477,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9noycr</t>
+          <t>https://talk.naver.com/ct/w4r74y</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1487,17 +1491,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>487</v>
+        <v>420</v>
       </c>
       <c r="Q11" t="n">
-        <v>62</v>
+        <v>2121</v>
       </c>
       <c r="R11" t="n">
-        <v>549</v>
+        <v>2541</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,309 +1510,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1934353498</t>
+          <t>1113071233</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934353498</t>
+          <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>다이어트,비만</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>l860923l@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1356-4013</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>329</v>
-      </c>
-      <c r="R12" t="n">
-        <v>432</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1701902663</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>유케이 짐</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ukgym_official@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1399-1895</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxm7p20</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>236</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>137</v>
-      </c>
-      <c r="R13" t="n">
-        <v>373</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1054343439</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>hannover_reha@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1378-5757</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>대구 중구 공평로8길 11-1 3층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://hanover.co.kr</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r74y</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>420</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2120</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2540</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1113071233</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1113071233</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -624,10 +624,10 @@
         <v>346</v>
       </c>
       <c r="Q2" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="R2" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         <v>104</v>
       </c>
       <c r="Q3" t="n">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="R3" t="n">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="Q4" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="R4" t="n">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -849,34 +849,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 몰리짐 장기점</t>
+          <t>시너지피트니스 수성점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mollygym_vol3@naver.com</t>
+          <t>gusalsdl903@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1469-9682</t>
+          <t>0507-1365-7677</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 달서구 용산로 80 에이동</t>
+          <t>대구 수성구 수성로75길 16 제401동 103호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mollygym_vol.3/</t>
+          <t>https://www.instagram.com/synergy.suseong</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t9mv</t>
+          <t>https://talk.naver.com/ct/we3e2hr</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1080</v>
+        <v>966</v>
       </c>
       <c r="Q5" t="n">
-        <v>546</v>
+        <v>1221</v>
       </c>
       <c r="R5" t="n">
-        <v>1626</v>
+        <v>2187</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1048460846</t>
+          <t>1125888116</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048460846</t>
+          <t>https://m.place.naver.com/place/1125888116</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1046,25 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레드짐 동성로점 헬스&amp;PT</t>
+          <t>짐 엘리트&amp;필라테스 진천점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>redgym_dongseongro@naver.com</t>
+          <t>gymelite@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1383-3968</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 중구 동성로2길 95 지하1, 2층 B101, B201호</t>
+          <t>대구 달서구 월배로15길 8 595b 5, 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/redgym_dongseongro</t>
+          <t>https://blog.naver.com/gymelite/224198604998</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1079,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1089,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xyzh</t>
+          <t>https://talk.naver.com/ct/w5usqm</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>395</v>
+        <v>175</v>
       </c>
       <c r="Q7" t="n">
-        <v>393</v>
+        <v>604</v>
       </c>
       <c r="R7" t="n">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1444163779</t>
+          <t>1097499417</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1444163779</t>
+          <t>https://m.place.naver.com/place/1097499417</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,34 +1144,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>몰리짐 중동교점</t>
+          <t>국민피티 월배점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mollygym@naver.com</t>
+          <t>kukminptwolbae@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1498-9683</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
+          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_lxhpxns</t>
+          <t>https://blog.naver.com/kukminptwolbae</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1177,22 +1177,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4muzo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1201,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>803</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>1269</v>
+        <v>184</v>
       </c>
       <c r="R8" t="n">
-        <v>2072</v>
+        <v>211</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1212,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1614047956</t>
+          <t>1009333460</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614047956</t>
+          <t>https://m.place.naver.com/place/1009333460</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1233,34 +1229,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>비무브짐24 헬스&amp;PT 상인점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>skyseung2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1469-7950</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 달서구 월곡로 219 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://blog.naver.com/skyseung2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,7 +1271,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1281,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/w5i8k0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>103</v>
+        <v>964</v>
       </c>
       <c r="Q9" t="n">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="R9" t="n">
-        <v>432</v>
+        <v>1264</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1310,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>1215597139</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/1215597139</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1331,34 +1327,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유케이 짐</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ukgym_official@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1399-1895</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ukgym_official</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,7 +1369,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1379,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxm7p20</t>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>236</v>
+        <v>103</v>
       </c>
       <c r="Q10" t="n">
-        <v>137</v>
+        <v>329</v>
       </c>
       <c r="R10" t="n">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1408,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1054343439</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1434,91 +1430,189 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+          <t>유케이 짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hannover_reha@naver.com</t>
+          <t>ukgym_official@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1378-5757</t>
+          <t>0507-1399-1895</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ukgym_official</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>137</v>
+      </c>
+      <c r="R11" t="n">
+        <v>373</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1054343439</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054343439</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hannover_reha@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1378-5757</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://hanover.co.kr</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4r74y</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>420</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2121</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2541</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>421</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2123</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2544</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1113071233</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>노바짐 헬스&amp;PT 달서구점</t>
+          <t>마이핏피트니스 플래그십 월성점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nova__gym@naver.com</t>
+          <t>heesangi2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1378-9994</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 달서구 장기로 217 8, 9층</t>
+          <t>대구 달서구 월성로 79 2층전체</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nova__gym</t>
+          <t>https://blog.naver.com/heesangi2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ttpt</t>
+          <t>https://talk.naver.com/ct/w677q25</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>346</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="n">
-        <v>443</v>
+        <v>619</v>
       </c>
       <c r="R2" t="n">
-        <v>789</v>
+        <v>723</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1731760179</t>
+          <t>2074789520</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1731760179</t>
+          <t>https://m.place.naver.com/place/2074789520</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마이핏피트니스 플래그십 월성점</t>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>heesangi2@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1378-9994</t>
+          <t>0507-1341-2034</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구 달서구 월성로 79 2층전체</t>
+          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heesangi2</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w677q25</t>
+          <t>https://talk.naver.com/ct/wdal64e</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>104</v>
+        <v>1196</v>
       </c>
       <c r="Q3" t="n">
-        <v>615</v>
+        <v>557</v>
       </c>
       <c r="R3" t="n">
-        <v>719</v>
+        <v>1753</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2074789520</t>
+          <t>671730517</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074789520</t>
+          <t>https://m.place.naver.com/place/671730517</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
+          <t>시너지피트니스 수성점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atmhjqnib@naver.com</t>
+          <t>gusalsdl903@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1341-2034</t>
+          <t>0507-1365-7677</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
+          <t>대구 수성구 수성로75길 16 제401동 103호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atmhjqnib</t>
+          <t>https://www.instagram.com/synergy.suseong</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdal64e</t>
+          <t>https://talk.naver.com/ct/we3e2hr</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1196</v>
+        <v>966</v>
       </c>
       <c r="Q4" t="n">
-        <v>557</v>
+        <v>1221</v>
       </c>
       <c r="R4" t="n">
-        <v>1753</v>
+        <v>2187</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>671730517</t>
+          <t>1125888116</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/671730517</t>
+          <t>https://m.place.naver.com/place/1125888116</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>시너지피트니스 수성점</t>
+          <t>지젤 칠곡점 헬스 PT GX 요가</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gusalsdl903@naver.com</t>
+          <t>giselle331704@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1365-7677</t>
+          <t>0507-1321-6496</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 수성구 수성로75길 16 제401동 103호</t>
+          <t>대구 북구 동암로 90 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/synergy.suseong</t>
+          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,14 +900,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/we3e2hr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>966</v>
+        <v>1241</v>
       </c>
       <c r="Q5" t="n">
-        <v>1221</v>
+        <v>544</v>
       </c>
       <c r="R5" t="n">
-        <v>2187</v>
+        <v>1785</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1125888116</t>
+          <t>1616049160</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125888116</t>
+          <t>https://m.place.naver.com/place/1616049160</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -952,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+          <t>짐 엘리트&amp;필라테스 진천점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>giselle331704@naver.com</t>
+          <t>gymelite@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1321-6496</t>
+          <t>0507-1383-3968</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 북구 동암로 90 3층</t>
+          <t>대구 달서구 월배로15길 8 595b 5, 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>https://blog.naver.com/gymelite/224198604998</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,15 +989,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5usqm</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1009,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1241</v>
+        <v>175</v>
       </c>
       <c r="Q6" t="n">
-        <v>544</v>
+        <v>604</v>
       </c>
       <c r="R6" t="n">
-        <v>1785</v>
+        <v>779</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1616049160</t>
+          <t>1097499417</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616049160</t>
+          <t>https://m.place.naver.com/place/1097499417</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1046,29 +1050,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐 엘리트&amp;필라테스 진천점</t>
+          <t>국민피티 월배점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gymelite@naver.com</t>
+          <t>kukminptwolbae@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1383-3968</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로15길 8 595b 5, 6층</t>
+          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymelite/224198604998</t>
+          <t>https://blog.naver.com/kukminptwolbae</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1088,14 +1088,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5usqm</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>604</v>
+        <v>184</v>
       </c>
       <c r="R7" t="n">
-        <v>779</v>
+        <v>211</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1097499417</t>
+          <t>1009333460</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097499417</t>
+          <t>https://m.place.naver.com/place/1009333460</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1144,25 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>국민피티 월배점</t>
+          <t>비무브짐24 헬스&amp;PT 상인점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kukminptwolbae@naver.com</t>
+          <t>skyseung2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1469-7950</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
+          <t>대구 달서구 월곡로 219 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kukminptwolbae</t>
+          <t>https://blog.naver.com/skyseung2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1182,10 +1182,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8k0</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1197,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>964</v>
       </c>
       <c r="Q8" t="n">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="R8" t="n">
-        <v>211</v>
+        <v>1264</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1009333460</t>
+          <t>1215597139</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
+          <t>https://m.place.naver.com/place/1215597139</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1234,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 상인점</t>
+          <t>피크짐 신천점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skyseung2@naver.com</t>
+          <t>peakgym2022@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1469-7950</t>
+          <t>0507-1355-6339</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 달서구 월곡로 219 4층</t>
+          <t>대구 동구 장등로 66 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skyseung2</t>
+          <t>https://blog.naver.com/peakgym2022</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1281,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i8k0</t>
+          <t>https://talk.naver.com/ct/w9noycr</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>964</v>
+        <v>488</v>
       </c>
       <c r="Q9" t="n">
-        <v>300</v>
+        <v>62</v>
       </c>
       <c r="R9" t="n">
-        <v>1264</v>
+        <v>550</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,51 +1314,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1215597139</t>
+          <t>1934353498</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215597139</t>
+          <t>https://m.place.naver.com/place/1934353498</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>소울휘트니스 시지점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>younae04@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1374-7045</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 수성구 고산로 121 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://open.kakao.com/o/s0jMm2qi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1379,12 +1383,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/w5tubr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1393,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>103</v>
+        <v>366</v>
       </c>
       <c r="Q10" t="n">
-        <v>329</v>
+        <v>481</v>
       </c>
       <c r="R10" t="n">
-        <v>432</v>
+        <v>847</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,51 +1412,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>13521393</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/13521393</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유케이 짐</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ukgym_official@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-1895</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ukgym_official</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1477,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxm7p20</t>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1491,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>236</v>
+        <v>103</v>
       </c>
       <c r="Q11" t="n">
-        <v>137</v>
+        <v>329</v>
       </c>
       <c r="R11" t="n">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1054343439</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1528,93 +1532,289 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+          <t>유케이 짐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hannover_reha@naver.com</t>
+          <t>ukgym_official@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1378-5757</t>
+          <t>0507-1399-1895</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ukgym_official</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>137</v>
+      </c>
+      <c r="R12" t="n">
+        <v>373</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1054343439</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054343439</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>워너비핏</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>wannabefit2400@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1407-2402</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대구 수성구 달구벌대로 2317 . 105동 지하1층 비1호(수성동4 가, 우방사랑마을아파트)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wannabefit2400</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ykq</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>123</v>
+      </c>
+      <c r="R13" t="n">
+        <v>249</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1742130217</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1742130217</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hannover_reha@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1378-5757</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://hanover.co.kr</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4r74y</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>421</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q14" t="n">
         <v>2123</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R14" t="n">
         <v>2544</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>1113071233</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마이핏피트니스 플래그십 월성점</t>
+          <t>노바짐 헬스&amp;PT 달서구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>heesangi2@naver.com</t>
+          <t>nova__gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1378-9994</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 달서구 월성로 79 2층전체</t>
+          <t>대구 달서구 장기로 217 8, 9층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heesangi2</t>
+          <t>https://blog.naver.com/nova__gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +607,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w677q25</t>
+          <t>https://talk.naver.com/ct/w5ttpt</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>104</v>
+        <v>346</v>
       </c>
       <c r="Q2" t="n">
-        <v>619</v>
+        <v>444</v>
       </c>
       <c r="R2" t="n">
-        <v>723</v>
+        <v>790</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2074789520</t>
+          <t>1731760179</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074789520</t>
+          <t>https://m.place.naver.com/place/1731760179</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
+          <t>마이핏피트니스 플래그십 월성점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atmhjqnib@naver.com</t>
+          <t>heesangi2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1341-2034</t>
+          <t>0507-1378-9994</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
+          <t>대구 달서구 월성로 79 2층전체</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atmhjqnib</t>
+          <t>https://blog.naver.com/heesangi2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdal64e</t>
+          <t>https://talk.naver.com/ct/w677q25</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1196</v>
+        <v>104</v>
       </c>
       <c r="Q3" t="n">
-        <v>557</v>
+        <v>633</v>
       </c>
       <c r="R3" t="n">
-        <v>1753</v>
+        <v>737</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>671730517</t>
+          <t>2074789520</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/671730517</t>
+          <t>https://m.place.naver.com/place/2074789520</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>시너지피트니스 수성점</t>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gusalsdl903@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1365-7677</t>
+          <t>0507-1341-2034</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 수성구 수성로75길 16 제401동 103호</t>
+          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/synergy.suseong</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we3e2hr</t>
+          <t>https://talk.naver.com/ct/wdal64e</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>966</v>
+        <v>1197</v>
       </c>
       <c r="Q4" t="n">
-        <v>1221</v>
+        <v>557</v>
       </c>
       <c r="R4" t="n">
-        <v>2187</v>
+        <v>1754</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1125888116</t>
+          <t>671730517</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125888116</t>
+          <t>https://m.place.naver.com/place/671730517</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>지젤 칠곡점 헬스 PT GX 요가</t>
+          <t>시너지피트니스 수성점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>giselle331704@naver.com</t>
+          <t>gusalsdl903@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1321-6496</t>
+          <t>0507-1365-7677</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 북구 동암로 90 3층</t>
+          <t>대구 수성구 수성로75길 16 제401동 103호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/giselle_chilgok/?next=%2F</t>
+          <t>https://www.instagram.com/synergy.suseong</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/we3e2hr</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1241</v>
+        <v>968</v>
       </c>
       <c r="Q5" t="n">
-        <v>544</v>
+        <v>1219</v>
       </c>
       <c r="R5" t="n">
-        <v>1785</v>
+        <v>2187</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1616049160</t>
+          <t>1125888116</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616049160</t>
+          <t>https://m.place.naver.com/place/1125888116</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q6" t="n">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="R6" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1045,30 +1045,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>국민피티 월배점</t>
+          <t>헬스&amp;PT 몰리짐 장기점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kukminptwolbae@naver.com</t>
+          <t>mollygym_vol3@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1469-9682</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
+          <t>대구 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kukminptwolbae</t>
+          <t>https://www.instagram.com/mollygym_vol.3/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,15 +1087,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t9mv</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1103,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>27</v>
+        <v>1087</v>
       </c>
       <c r="Q7" t="n">
-        <v>184</v>
+        <v>547</v>
       </c>
       <c r="R7" t="n">
-        <v>211</v>
+        <v>1634</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1009333460</t>
+          <t>1048460846</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
+          <t>https://m.place.naver.com/place/1048460846</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 상인점</t>
+          <t>몰리짐 중동교점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>skyseung2@naver.com</t>
+          <t>mollygym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1469-7950</t>
+          <t>0507-1498-9683</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 달서구 월곡로 219 4층</t>
+          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skyseung2</t>
+          <t>http://pf.kakao.com/_lxhpxns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1177,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1187,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i8k0</t>
+          <t>https://talk.naver.com/ct/w4muzo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1201,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>806</v>
       </c>
       <c r="Q8" t="n">
-        <v>300</v>
+        <v>1269</v>
       </c>
       <c r="R8" t="n">
-        <v>1264</v>
+        <v>2075</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1215597139</t>
+          <t>1614047956</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215597139</t>
+          <t>https://m.place.naver.com/place/1614047956</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,29 +1246,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피크짐 신천점</t>
+          <t>국민피티 월배점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>peakgym2022@naver.com</t>
+          <t>kukminptwolbae@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1355-6339</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 동구 장등로 66 1층</t>
+          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/peakgym2022</t>
+          <t>https://blog.naver.com/kukminptwolbae</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1280,14 +1284,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9noycr</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,17 +1295,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>488</v>
+        <v>27</v>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>184</v>
       </c>
       <c r="R9" t="n">
-        <v>550</v>
+        <v>211</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1934353498</t>
+          <t>1009333460</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934353498</t>
+          <t>https://m.place.naver.com/place/1009333460</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1331,34 +1331,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>소울휘트니스 시지점</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>younae04@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1374-7045</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 고산로 121 2층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s0jMm2qi</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tubr</t>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>366</v>
+        <v>103</v>
       </c>
       <c r="Q10" t="n">
-        <v>481</v>
+        <v>329</v>
       </c>
       <c r="R10" t="n">
-        <v>847</v>
+        <v>432</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13521393</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13521393</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1429,34 +1429,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>유케이 짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>ukgym_official@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1399-1895</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://blog.naver.com/ukgym_official</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>103</v>
+        <v>236</v>
       </c>
       <c r="Q11" t="n">
-        <v>329</v>
+        <v>137</v>
       </c>
       <c r="R11" t="n">
-        <v>432</v>
+        <v>373</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>1054343439</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/1054343439</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1532,29 +1532,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>유케이 짐</t>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ukgym_official@naver.com</t>
+          <t>hannover_reha@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1399-1895</t>
+          <t>0507-1378-5757</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+          <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ukgym_official</t>
+          <t>https://hanover.co.kr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxm7p20</t>
+          <t>https://talk.naver.com/ct/w4r74y</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>236</v>
+        <v>421</v>
       </c>
       <c r="Q12" t="n">
-        <v>137</v>
+        <v>2128</v>
       </c>
       <c r="R12" t="n">
-        <v>373</v>
+        <v>2549</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1608,211 +1608,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1054343439</t>
+          <t>1113071233</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
+          <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>워너비핏</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>wannabefit2400@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1407-2402</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대구 수성구 달구벌대로 2317 . 105동 지하1층 비1호(수성동4 가, 우방사랑마을아파트)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/wannabefit2400</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40ykq</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>126</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>123</v>
-      </c>
-      <c r="R13" t="n">
-        <v>249</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1742130217</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1742130217</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>hannover_reha@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1378-5757</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>대구 중구 공평로8길 11-1 3층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://hanover.co.kr</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r74y</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>421</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2123</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2544</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1113071233</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1113071233</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>노바짐 헬스&amp;PT 달서구점</t>
+          <t>마이핏피트니스 플래그십 월성점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nova__gym@naver.com</t>
+          <t>heesangi2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0507-1378-9994</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 달서구 장기로 217 8, 9층</t>
+          <t>대구 달서구 월성로 79 2층전체</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nova__gym</t>
+          <t>https://blog.naver.com/heesangi2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -607,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ttpt</t>
+          <t>https://talk.naver.com/ct/w677q25</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>346</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="n">
-        <v>444</v>
+        <v>636</v>
       </c>
       <c r="R2" t="n">
-        <v>790</v>
+        <v>740</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1731760179</t>
+          <t>2074789520</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1731760179</t>
+          <t>https://m.place.naver.com/place/2074789520</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마이핏피트니스 플래그십 월성점</t>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>heesangi2@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1378-9994</t>
+          <t>0507-1341-2034</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구 달서구 월성로 79 2층전체</t>
+          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heesangi2</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w677q25</t>
+          <t>https://talk.naver.com/ct/wdal64e</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>104</v>
+        <v>1198</v>
       </c>
       <c r="Q3" t="n">
-        <v>633</v>
+        <v>557</v>
       </c>
       <c r="R3" t="n">
-        <v>737</v>
+        <v>1755</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2074789520</t>
+          <t>671730517</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074789520</t>
+          <t>https://m.place.naver.com/place/671730517</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
+          <t>시너지피트니스 수성점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atmhjqnib@naver.com</t>
+          <t>gusalsdl903@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1341-2034</t>
+          <t>0507-1365-7677</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
+          <t>대구 수성구 수성로75길 16 제401동 103호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atmhjqnib</t>
+          <t>https://www.instagram.com/synergy.suseong</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdal64e</t>
+          <t>https://talk.naver.com/ct/we3e2hr</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1197</v>
+        <v>968</v>
       </c>
       <c r="Q4" t="n">
-        <v>557</v>
+        <v>1219</v>
       </c>
       <c r="R4" t="n">
-        <v>1754</v>
+        <v>2187</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>671730517</t>
+          <t>1125888116</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/671730517</t>
+          <t>https://m.place.naver.com/place/1125888116</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>시너지피트니스 수성점</t>
+          <t>짐 엘리트&amp;필라테스 진천점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gusalsdl903@naver.com</t>
+          <t>gymelite@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1365-7677</t>
+          <t>0507-1383-3968</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 수성구 수성로75길 16 제401동 103호</t>
+          <t>대구 달서구 월배로15길 8 595b 5, 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/synergy.suseong</t>
+          <t>https://blog.naver.com/gymelite/224198604998</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we3e2hr</t>
+          <t>https://talk.naver.com/ct/w5usqm</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>968</v>
+        <v>174</v>
       </c>
       <c r="Q5" t="n">
-        <v>1219</v>
+        <v>614</v>
       </c>
       <c r="R5" t="n">
-        <v>2187</v>
+        <v>788</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,51 +934,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1125888116</t>
+          <t>1097499417</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125888116</t>
+          <t>https://m.place.naver.com/place/1097499417</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐 엘리트&amp;필라테스 진천점</t>
+          <t>헬스&amp;PT 몰리짐 장기점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gymelite@naver.com</t>
+          <t>mollygym_vol3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1383-3968</t>
+          <t>0507-1469-9682</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로15길 8 595b 5, 6층</t>
+          <t>대구 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymelite/224198604998</t>
+          <t>https://www.instagram.com/mollygym_vol.3/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5usqm</t>
+          <t>https://talk.naver.com/ct/w5t9mv</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>174</v>
+        <v>1087</v>
       </c>
       <c r="Q6" t="n">
-        <v>614</v>
+        <v>548</v>
       </c>
       <c r="R6" t="n">
-        <v>788</v>
+        <v>1635</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,56 +1032,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1097499417</t>
+          <t>1048460846</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097499417</t>
+          <t>https://m.place.naver.com/place/1048460846</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 몰리짐 장기점</t>
+          <t>몰리짐 중동교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mollygym_vol3@naver.com</t>
+          <t>mollygym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1469-9682</t>
+          <t>0507-1498-9683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 달서구 용산로 80 에이동</t>
+          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mollygym_vol.3/</t>
+          <t>http://pf.kakao.com/_lxhpxns</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1097,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t9mv</t>
+          <t>https://talk.naver.com/ct/w4muzo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1087</v>
+        <v>806</v>
       </c>
       <c r="Q7" t="n">
-        <v>547</v>
+        <v>1269</v>
       </c>
       <c r="R7" t="n">
-        <v>1634</v>
+        <v>2075</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1048460846</t>
+          <t>1614047956</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048460846</t>
+          <t>https://m.place.naver.com/place/1614047956</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1152,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>몰리짐 중동교점</t>
+          <t>국민피티 월배점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mollygym@naver.com</t>
+          <t>kukminptwolbae@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1498-9683</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
+          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_lxhpxns</t>
+          <t>https://blog.naver.com/kukminptwolbae</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,22 +1185,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4muzo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>806</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>1269</v>
+        <v>184</v>
       </c>
       <c r="R8" t="n">
-        <v>2075</v>
+        <v>211</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1614047956</t>
+          <t>1009333460</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614047956</t>
+          <t>https://m.place.naver.com/place/1009333460</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1246,25 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>국민피티 월배점</t>
+          <t>비무브짐24 헬스&amp;PT 상인점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kukminptwolbae@naver.com</t>
+          <t>skyseung2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1469-7950</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
+          <t>대구 달서구 월곡로 219 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kukminptwolbae</t>
+          <t>https://blog.naver.com/skyseung2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1284,10 +1284,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i8k0</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>964</v>
       </c>
       <c r="Q9" t="n">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="R9" t="n">
-        <v>211</v>
+        <v>1264</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,51 +1318,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1009333460</t>
+          <t>1215597139</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
+          <t>https://m.place.naver.com/place/1215597139</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>피크짐 신천점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>peakgym2022@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1355-6339</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 동구 장등로 66 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://blog.naver.com/peakgym2022</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/w9noycr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1393,17 +1397,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>103</v>
+        <v>490</v>
       </c>
       <c r="Q10" t="n">
-        <v>329</v>
+        <v>62</v>
       </c>
       <c r="R10" t="n">
-        <v>432</v>
+        <v>552</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,51 +1416,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>1934353498</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/1934353498</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유케이 짐</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ukgym_official@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1399-1895</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ukgym_official</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1481,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wxm7p20</t>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>236</v>
+        <v>103</v>
       </c>
       <c r="Q11" t="n">
-        <v>137</v>
+        <v>329</v>
       </c>
       <c r="R11" t="n">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1054343439</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1532,93 +1536,191 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+          <t>유케이 짐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hannover_reha@naver.com</t>
+          <t>ukgym_official@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1378-5757</t>
+          <t>0507-1399-1895</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ukgym_official</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>137</v>
+      </c>
+      <c r="R12" t="n">
+        <v>373</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1054343439</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054343439</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hannover_reha@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1378-5757</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://hanover.co.kr</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w4r74y</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>421</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q13" t="n">
         <v>2128</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R13" t="n">
         <v>2549</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>1113071233</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/대구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/대구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마이핏피트니스 플래그십 월성점</t>
+          <t>노바짐 헬스&amp;PT 달서구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>heesangi2@naver.com</t>
+          <t>nova__gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1378-9994</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구 달서구 월성로 79 2층전체</t>
+          <t>대구 달서구 장기로 217 8, 9층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heesangi2</t>
+          <t>https://blog.naver.com/nova__gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +607,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w677q25</t>
+          <t>https://talk.naver.com/ct/w5ttpt</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>104</v>
+        <v>346</v>
       </c>
       <c r="Q2" t="n">
-        <v>636</v>
+        <v>444</v>
       </c>
       <c r="R2" t="n">
-        <v>740</v>
+        <v>790</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2074789520</t>
+          <t>1731760179</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2074789520</t>
+          <t>https://m.place.naver.com/place/1731760179</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
+          <t>마이핏피트니스 플래그십 월성점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atmhjqnib@naver.com</t>
+          <t>heesangi2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1341-2034</t>
+          <t>0507-1378-9994</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
+          <t>대구 달서구 월성로 79 2층전체</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atmhjqnib</t>
+          <t>https://blog.naver.com/heesangi2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdal64e</t>
+          <t>https://talk.naver.com/ct/w677q25</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1198</v>
+        <v>104</v>
       </c>
       <c r="Q3" t="n">
-        <v>557</v>
+        <v>639</v>
       </c>
       <c r="R3" t="n">
-        <v>1755</v>
+        <v>743</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>671730517</t>
+          <t>2074789520</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/671730517</t>
+          <t>https://m.place.naver.com/place/2074789520</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>시너지피트니스 수성점</t>
+          <t>지젤 범어점 헬스 PT GX &amp; 스파</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gusalsdl903@naver.com</t>
+          <t>atmhjqnib@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1365-7677</t>
+          <t>0507-1341-2034</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구 수성구 수성로75길 16 제401동 103호</t>
+          <t>대구 수성구 달구벌대로 2382-1 지하1층, 지상4층, 지상5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/synergy.suseong</t>
+          <t>https://blog.naver.com/atmhjqnib</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/we3e2hr</t>
+          <t>https://talk.naver.com/ct/wdal64e</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>968</v>
+        <v>1198</v>
       </c>
       <c r="Q4" t="n">
-        <v>1219</v>
+        <v>557</v>
       </c>
       <c r="R4" t="n">
-        <v>2187</v>
+        <v>1755</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1125888116</t>
+          <t>671730517</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125888116</t>
+          <t>https://m.place.naver.com/place/671730517</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>짐 엘리트&amp;필라테스 진천점</t>
+          <t>시너지피트니스 수성점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gymelite@naver.com</t>
+          <t>gusalsdl903@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1383-3968</t>
+          <t>0507-1365-7677</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로15길 8 595b 5, 6층</t>
+          <t>대구 수성구 수성로75길 16 제401동 103호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymelite/224198604998</t>
+          <t>https://www.instagram.com/synergy.suseong</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +891,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5usqm</t>
+          <t>https://talk.naver.com/ct/we3e2hr</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>174</v>
+        <v>968</v>
       </c>
       <c r="Q5" t="n">
-        <v>614</v>
+        <v>1219</v>
       </c>
       <c r="R5" t="n">
-        <v>788</v>
+        <v>2187</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1097499417</t>
+          <t>1125888116</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1097499417</t>
+          <t>https://m.place.naver.com/place/1125888116</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -951,34 +947,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 몰리짐 장기점</t>
+          <t>짐 엘리트&amp;필라테스 진천점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mollygym_vol3@naver.com</t>
+          <t>gymelite@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1469-9682</t>
+          <t>0507-1383-3968</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 달서구 용산로 80 에이동</t>
+          <t>대구 달서구 월배로15길 8 595b 5, 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mollygym_vol.3/</t>
+          <t>https://blog.naver.com/gymelite/224198604998</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t9mv</t>
+          <t>https://talk.naver.com/ct/w5usqm</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1087</v>
+        <v>174</v>
       </c>
       <c r="Q6" t="n">
-        <v>548</v>
+        <v>624</v>
       </c>
       <c r="R6" t="n">
-        <v>1635</v>
+        <v>798</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1048460846</t>
+          <t>1097499417</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048460846</t>
+          <t>https://m.place.naver.com/place/1097499417</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1049,39 +1045,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>몰리짐 중동교점</t>
+          <t>헬스&amp;PT 몰리짐 장기점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mollygym@naver.com</t>
+          <t>mollygym_vol3@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1498-9683</t>
+          <t>0507-1469-9682</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
+          <t>대구 달서구 용산로 80 에이동</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_lxhpxns</t>
+          <t>https://www.instagram.com/mollygym_vol.3/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4muzo</t>
+          <t>https://talk.naver.com/ct/w5t9mv</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>806</v>
+        <v>1087</v>
       </c>
       <c r="Q7" t="n">
-        <v>1269</v>
+        <v>548</v>
       </c>
       <c r="R7" t="n">
-        <v>2075</v>
+        <v>1635</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1614047956</t>
+          <t>1048460846</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614047956</t>
+          <t>https://m.place.naver.com/place/1048460846</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,30 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>국민피티 월배점</t>
+          <t>몰리짐 중동교점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kukminptwolbae@naver.com</t>
+          <t>mollygym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1498-9683</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구 달서구 월배로 159 월배역디엘라온프라이빗 B101 국민피티</t>
+          <t>대구 남구 대봉로 12 A동 대로변상가 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kukminptwolbae</t>
+          <t>http://pf.kakao.com/_lxhpxns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1185,18 +1185,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4muzo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>806</v>
       </c>
       <c r="Q8" t="n">
-        <v>184</v>
+        <v>1269</v>
       </c>
       <c r="R8" t="n">
-        <v>211</v>
+        <v>2075</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1009333460</t>
+          <t>1614047956</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009333460</t>
+          <t>https://m.place.naver.com/place/1614047956</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1237,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비무브짐24 헬스&amp;PT 상인점</t>
+          <t>에이펙스 이엠에스 스튜디오 대구점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skyseung2@naver.com</t>
+          <t>l860923l@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1469-7950</t>
+          <t>0507-1356-4013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구 달서구 월곡로 219 4층</t>
+          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skyseung2</t>
+          <t>https://www.instagram.com/apexems2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i8k0</t>
+          <t>https://talk.naver.com/ct/w4r5eg</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>964</v>
+        <v>103</v>
       </c>
       <c r="Q9" t="n">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="R9" t="n">
-        <v>1264</v>
+        <v>432</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1215597139</t>
+          <t>1701902663</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215597139</t>
+          <t>https://m.place.naver.com/place/1701902663</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피크짐 신천점</t>
+          <t>유케이 짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>peakgym2022@naver.com</t>
+          <t>ukgym_official@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1355-6339</t>
+          <t>0507-1399-1895</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구 동구 장등로 66 1층</t>
+          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/peakgym2022</t>
+          <t>https://blog.naver.com/ukgym_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9noycr</t>
+          <t>https://talk.naver.com/ct/wxm7p20</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1397,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>490</v>
+        <v>236</v>
       </c>
       <c r="Q10" t="n">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="R10" t="n">
-        <v>552</v>
+        <v>373</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1934353498</t>
+          <t>1054343439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934353498</t>
+          <t>https://m.place.naver.com/place/1054343439</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1433,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 대구점</t>
+          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>l860923l@naver.com</t>
+          <t>hannover_reha@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1356-4013</t>
+          <t>0507-1378-5757</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구 수성구 상록로 15 판매시설동 1층 163호 에이펙스 이엠에스 스튜디오</t>
+          <t>대구 중구 공평로8길 11-1 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/apexems2</t>
+          <t>https://hanover.co.kr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r5eg</t>
+          <t>https://talk.naver.com/ct/w4r74y</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>103</v>
+        <v>421</v>
       </c>
       <c r="Q11" t="n">
-        <v>329</v>
+        <v>2128</v>
       </c>
       <c r="R11" t="n">
-        <v>432</v>
+        <v>2549</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,211 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1701902663</t>
+          <t>1113071233</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701902663</t>
+          <t>https://m.place.naver.com/place/1113071233</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>유케이 짐</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ukgym_official@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1399-1895</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>대구 달서구 달구벌대로309길 13 지하1층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ukgym_official</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wxm7p20</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>236</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>137</v>
-      </c>
-      <c r="R12" t="n">
-        <v>373</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1054343439</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1054343439</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>하노버 메디칼 운동센터 &amp; 재활PT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>hannover_reha@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1378-5757</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>대구 중구 공평로8길 11-1 3층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://hanover.co.kr</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4r74y</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>421</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2128</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2549</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1113071233</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1113071233</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
